--- a/output/pdf_financials_xlsx/KMP.UN.xlsx
+++ b/output/pdf_financials_xlsx/KMP.UN.xlsx
@@ -1892,25 +1892,25 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>18.847</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>11.673</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.789</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>6.484</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>14.087</v>
@@ -1980,25 +1980,25 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>18.847</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>11.673</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.789</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>6.484</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>14.087</v>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/output/pdf_financials_xlsx/KMP.UN.xlsx
+++ b/output/pdf_financials_xlsx/KMP.UN.xlsx
@@ -5393,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="113">
@@ -16827,7 +16827,11 @@
           <t>Proceeds on disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KMP.UN.xlsx
+++ b/output/pdf_financials_xlsx/KMP.UN.xlsx
@@ -2878,31 +2878,31 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>9.391</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>10.275</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>11.231</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>12.557</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>16.721</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>17.238</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>19.764</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>20.276</v>
       </c>
     </row>
     <row r="57">
@@ -2922,31 +2922,31 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>3.616</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>4.418</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>5.302</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>6.039</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>6.898</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>9.359</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>9.91</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>10.629</v>
       </c>
     </row>
     <row r="58">
